--- a/data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_fob.xlsx
+++ b/data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_fob.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,7 +1013,7 @@
         <v>46053</v>
       </c>
       <c r="B74" t="n">
-        <v>1843157505</v>
+        <v>1843476386</v>
       </c>
     </row>
     <row r="75">
@@ -1021,7 +1021,7 @@
         <v>46081</v>
       </c>
       <c r="B75" t="n">
-        <v>1840522680</v>
+        <v>1833120931</v>
       </c>
     </row>
     <row r="76">
@@ -1029,7 +1029,7 @@
         <v>46112</v>
       </c>
       <c r="B76" t="n">
-        <v>1779291584</v>
+        <v>1774813115</v>
       </c>
     </row>
     <row r="77">
@@ -1037,7 +1037,7 @@
         <v>46142</v>
       </c>
       <c r="B77" t="n">
-        <v>2137280898</v>
+        <v>2115096466</v>
       </c>
     </row>
     <row r="78">
@@ -1045,7 +1045,7 @@
         <v>46173</v>
       </c>
       <c r="B78" t="n">
-        <v>1683117561</v>
+        <v>1657447109</v>
       </c>
     </row>
     <row r="79">
@@ -1053,7 +1053,7 @@
         <v>46203</v>
       </c>
       <c r="B79" t="n">
-        <v>2569324747</v>
+        <v>2561140623</v>
       </c>
     </row>
     <row r="80">
@@ -1061,7 +1061,7 @@
         <v>46234</v>
       </c>
       <c r="B80" t="n">
-        <v>2131758139</v>
+        <v>2132007782</v>
       </c>
     </row>
     <row r="81">
@@ -1069,7 +1069,15 @@
         <v>46265</v>
       </c>
       <c r="B81" t="n">
-        <v>2051566400</v>
+        <v>2037904434</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1771842975</v>
       </c>
     </row>
   </sheetData>
